--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261016.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20261016.xlsx
@@ -1327,17 +1327,17 @@
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>AEIS US</t>
+          <t>CMS US</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>艾儀有限公司</t>
+          <t>CMS能源</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>8,904</t>
+          <t>30,891</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1349,17 +1349,17 @@
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>CMS US</t>
+          <t>AEIS US</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>CMS能源</t>
+          <t>艾儀有限公司</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>30,891</t>
+          <t>8,904</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
@@ -1415,17 +1415,17 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>CNP US</t>
+          <t>LNT US</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>Centerpoint能源</t>
+          <t>聯合能源公司</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>43,783</t>
+          <t>25,881</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1437,17 +1437,17 @@
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>LNT US</t>
+          <t>CNP US</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>聯合能源公司</t>
+          <t>Centerpoint能源</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>25,881</t>
+          <t>43,783</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
